--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487755_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487755_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8976</v>
+        <v>7.0527</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6296</v>
+        <v>3.4304</v>
       </c>
       <c r="F2" t="n">
-        <v>3.268</v>
+        <v>3.6223</v>
       </c>
       <c r="G2" t="n">
         <v>7.2894</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6918</v>
+        <v>-0.5367</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.393</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2988</v>
+        <v>0.0556</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9404</v>
+        <v>5.1133</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5678</v>
+        <v>4.768</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3726</v>
+        <v>0.3453</v>
       </c>
       <c r="G3" t="n">
         <v>6.5673</v>
@@ -688,13 +688,13 @@
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2851</v>
+        <v>-0.1122</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3017</v>
+        <v>-0.1015</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0166</v>
+        <v>-0.0106</v>
       </c>
       <c r="V3" t="n">
         <v>-2.1179</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7017</v>
+        <v>1.5814</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8158</v>
+        <v>-1.0002</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5175</v>
+        <v>2.5815</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2172</v>
+        <v>0.5114</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5242</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.307</v>
+        <v>0.4299</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2075</v>
+        <v>-0.2436</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6313</v>
+        <v>-0.2842</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4237</v>
+        <v>0.0406</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1071</v>
+        <v>0.3658</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1168</v>
+        <v>0.3893</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2985</v>
+        <v>-0.194</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4248</v>
+        <v>-0.3942</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2752</v>
+        <v>-0.5625</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1497</v>
+        <v>0.1683</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. RODRÍGUEZ MACHÍN</t>
+          <t>P. RODRIGUEZ RIVERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6605</v>
+        <v>1.3948</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9211</v>
+        <v>-1.3569</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5815</v>
+        <v>2.7517</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5114</v>
+        <v>0.5695</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0824</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4299</v>
+        <v>0.4872</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2436</v>
+        <v>0.3599</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2842</v>
+        <v>0.3955</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0406</v>
+        <v>-0.0356</v>
       </c>
       <c r="M5" t="n">
-        <v>0.755</v>
+        <v>0.2096</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3658</v>
+        <v>-0.3131</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3893</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3152</v>
+        <v>-0.6912</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4834</v>
+        <v>-0.7108</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1683</v>
+        <v>0.0197</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2821</v>
+        <v>1.1283</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1283</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.058</v>
+        <v>0.909</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4781</v>
+        <v>-1.8179</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5361</v>
+        <v>2.7269</v>
       </c>
       <c r="G6" t="n">
         <v>1.0879</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3582</v>
+        <v>0.2092</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6079</v>
+        <v>0.268</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2496</v>
+        <v>-0.0589</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ RIVERO</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9639</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9786</v>
+        <v>-0.2351</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9425</v>
+        <v>0.8192</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5695</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0824</v>
+        <v>0.1862</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4872</v>
+        <v>0.7891</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3599</v>
+        <v>0.7315</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3955</v>
+        <v>0.6097</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0356</v>
+        <v>0.1218</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2096</v>
+        <v>0.2439</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3131</v>
+        <v>-0.4235</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6673</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5224</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.122</v>
+        <v>-0.0031</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3325</v>
+        <v>0.0036</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2104</v>
+        <v>-0.0067</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1283</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1283</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.83</v>
+        <v>0.5241</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.8286</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7647</v>
+        <v>1.3527</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1862</v>
+        <v>0.2447</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7891</v>
+        <v>-0.1451</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7315</v>
+        <v>-0.4837</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6097</v>
+        <v>0.0618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1218</v>
+        <v>-0.5455</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2439</v>
+        <v>0.5833</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4235</v>
+        <v>0.1829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6673</v>
+        <v>0.4004</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2427</v>
+        <v>-0.7397</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3039</v>
+        <v>-0.3449</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0612</v>
+        <v>-0.3948</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JIMENEZ FERNANDEZ</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7909</v>
+        <v>0.3768</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6443</v>
+        <v>-1.5956</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4353</v>
+        <v>1.9724</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.892</v>
+        <v>1.2172</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3114</v>
+        <v>1.5242</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5806</v>
+        <v>-0.307</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9853</v>
+        <v>1.2075</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1236</v>
+        <v>1.6313</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1089</v>
+        <v>-0.4237</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.435</v>
+        <v>-0.1071</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5283</v>
+        <v>0.1168</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3881</v>
+        <v>-3.2985</v>
       </c>
       <c r="R9" t="n">
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9948</v>
+        <v>1.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.729</v>
+        <v>0.4954</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2658</v>
+        <v>0.6046</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>A. JIMENEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3784</v>
+        <v>0.351</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0288</v>
+        <v>-1.0843</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4072</v>
+        <v>1.4353</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09950000000000001</v>
+        <v>-0.892</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2447</v>
+        <v>-0.3114</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1451</v>
+        <v>-0.5806</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4837</v>
+        <v>-0.9853</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0618</v>
+        <v>0.1236</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5455</v>
+        <v>-1.1089</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5833</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1829</v>
+        <v>-0.435</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4004</v>
+        <v>0.5283</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8854</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5451</v>
+        <v>0.2891</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3403</v>
+        <v>0.2658</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4869</v>
+        <v>-0.8169</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8594</v>
+        <v>-2.2984</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3725</v>
+        <v>1.4815</v>
       </c>
       <c r="G11" t="n">
         <v>0.3372</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3584</v>
+        <v>-0.6884</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0296</v>
+        <v>-0.4686</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3288</v>
+        <v>-0.2198</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6597</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0253</v>
+        <v>-1.7557</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2993</v>
+        <v>-2.1387</v>
       </c>
       <c r="F12" t="n">
-        <v>0.274</v>
+        <v>0.383</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2192</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9704</v>
+        <v>-0.7007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5451</v>
+        <v>-0.3844</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4253</v>
+        <v>-0.3163</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6119</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.7092</v>
+        <v>15.3147</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7628</v>
+        <v>-4.1573</v>
       </c>
       <c r="F13" t="n">
-        <v>19.4719</v>
+        <v>19.4718</v>
       </c>
       <c r="G13" t="n">
         <v>16.5435</v>
       </c>
       <c r="H13" t="n">
-        <v>3.641699999999999</v>
+        <v>3.6417</v>
       </c>
       <c r="I13" t="n">
         <v>12.9022</v>
@@ -1444,10 +1444,10 @@
         <v>12.0549</v>
       </c>
       <c r="K13" t="n">
-        <v>5.075200000000001</v>
+        <v>5.0752</v>
       </c>
       <c r="L13" t="n">
-        <v>6.979699999999999</v>
+        <v>6.979700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>4.488700000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-1.4337</v>
       </c>
       <c r="O13" t="n">
-        <v>5.922400000000001</v>
+        <v>5.9224</v>
       </c>
       <c r="P13" t="n">
         <v>3.8806</v>
@@ -1468,13 +1468,13 @@
         <v>17.4628</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6078</v>
+        <v>-2.0021</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.714400000000001</v>
+        <v>-2.1088</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1068</v>
+        <v>0.1069</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1075</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6848</v>
+        <v>0.208</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2259</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5411</v>
+        <v>-0.4387</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6601</v>
+        <v>-1.2296</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2873</v>
+        <v>-0.9343</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.6271</v>
+        <v>-0.2953</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1034</v>
+        <v>1.3301</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8063</v>
+        <v>-0.5602</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7029</v>
+        <v>1.8903</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4433</v>
+        <v>-2.5596</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5191</v>
+        <v>-0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9242</v>
+        <v>-2.1856</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2485</v>
+        <v>0.3794</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2568</v>
+        <v>0.1988</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9917</v>
+        <v>0.1806</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5289</v>
+        <v>0.2031</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4288</v>
+        <v>1.1258</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9577</v>
+        <v>-0.9226</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4547</v>
+        <v>0.6601</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1845</v>
+        <v>3.2873</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2702</v>
+        <v>-2.6271</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3105</v>
+        <v>3.1034</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0134</v>
+        <v>3.8063</v>
       </c>
       <c r="L15" t="n">
         <v>-0.7029</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7652</v>
+        <v>-2.4433</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1979</v>
+        <v>-0.5191</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5673</v>
+        <v>-1.9242</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3717</v>
+        <v>0.7669</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7249</v>
+        <v>0.1567</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6102</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3993</v>
+        <v>-0.3913</v>
       </c>
       <c r="E16" t="n">
-        <v>0.947</v>
+        <v>0.0206</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5477</v>
+        <v>-0.4119</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2296</v>
+        <v>-0.2579</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9343</v>
+        <v>-0.3913</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2953</v>
+        <v>0.1335</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3301</v>
+        <v>0.0206</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5602</v>
+        <v>0.0206</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8903</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5596</v>
+        <v>-0.2785</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.374</v>
+        <v>-0.4119</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1856</v>
+        <v>0.1335</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5706</v>
+        <v>-0.1335</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4991</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0716</v>
+        <v>-0.1335</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>G. MORENO ABAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3913</v>
+        <v>-0.5361</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0206</v>
+        <v>-2.4113</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4119</v>
+        <v>1.8752</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2579</v>
+        <v>-2.6023</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3913</v>
+        <v>-1.361</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1335</v>
+        <v>-1.2413</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0206</v>
+        <v>-1.855</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0206</v>
+        <v>-0.5026</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.3524</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2785</v>
+        <v>-0.7473</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4119</v>
+        <v>-0.8585</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1335</v>
+        <v>0.1112</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.3582</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1335</v>
+        <v>0.0482</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.5563</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1335</v>
+        <v>0.6046</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MORENO ABAD</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7185</v>
+        <v>-0.9583</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8117</v>
+        <v>-2.5729</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0932</v>
+        <v>1.6146</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6023</v>
+        <v>-2.9398</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.361</v>
+        <v>-1.8792</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2413</v>
+        <v>-1.0606</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.855</v>
+        <v>-2.2044</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5026</v>
+        <v>-1.5777</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3524</v>
+        <v>-0.6267</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7473</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8585</v>
+        <v>-0.3015</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1112</v>
+        <v>-0.4338</v>
       </c>
       <c r="P18" t="n">
         <v>1.3582</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1341</v>
+        <v>-0.0364</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9567</v>
+        <v>-0.1744</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8226</v>
+        <v>0.138</v>
       </c>
       <c r="V18" t="n">
         <v>0.6597</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4601</v>
+        <v>-1.0633</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.261</v>
+        <v>-1.8302</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1991</v>
+        <v>0.7669</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.594</v>
+        <v>-1.4547</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8115</v>
+        <v>-0.1845</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7825</v>
+        <v>-1.2702</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5649</v>
+        <v>0.3105</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6055</v>
+        <v>1.0134</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0406</v>
+        <v>-0.7029</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.029</v>
+        <v>-1.7652</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.206</v>
+        <v>-1.1979</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.5673</v>
       </c>
       <c r="P19" t="n">
-        <v>0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R19" t="n">
-        <v>0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0601</v>
+        <v>0.7795</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3039</v>
+        <v>0.3235</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3641</v>
+        <v>0.456</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6132</v>
+        <v>-1.6058</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8104</v>
+        <v>-0.4612</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1971</v>
+        <v>-1.1446</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7917</v>
+        <v>-1.594</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7697</v>
+        <v>-0.8115</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.5614</v>
+        <v>-0.7825</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5779</v>
+        <v>-0.5649</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0103</v>
+        <v>-0.6055</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.5881</v>
+        <v>0.0406</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2138</v>
+        <v>-1.029</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2406</v>
+        <v>-0.206</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8845</v>
+        <v>-0.2058</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1683</v>
+        <v>0.1037</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0527</v>
+        <v>-0.3095</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9405</v>
+        <v>-1.64</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1735</v>
+        <v>-2.5101</v>
       </c>
       <c r="F21" t="n">
-        <v>1.233</v>
+        <v>0.8701</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9398</v>
+        <v>-1.7917</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8792</v>
+        <v>1.7697</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0606</v>
+        <v>-3.5614</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2044</v>
+        <v>-0.5779</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5777</v>
+        <v>2.0103</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6267</v>
+        <v>-2.5881</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-1.2138</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3015</v>
+        <v>-0.2406</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4338</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.5523</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.9105</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.3582</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-0.194</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.5523</v>
-      </c>
       <c r="S21" t="n">
-        <v>-1.0186</v>
+        <v>0.8577</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.775</v>
+        <v>0.132</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2436</v>
+        <v>0.7257</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6597</v>
+        <v>0.8462</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4253</v>
+        <v>-4.071</v>
       </c>
       <c r="E22" t="n">
         <v>-5.6255</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2002</v>
+        <v>1.5545</v>
       </c>
       <c r="G22" t="n">
         <v>0.4655</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0063</v>
+        <v>0.3606</v>
       </c>
       <c r="T22" t="n">
         <v>0.1469</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1406</v>
+        <v>0.2137</v>
       </c>
       <c r="V22" t="n">
         <v>1.506</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7731</v>
+        <v>-4.8543</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.5545</v>
+        <v>-5.8538</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7814</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7992</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1276</v>
+        <v>-0.2089</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1384</v>
+        <v>-0.4377</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0108</v>
+        <v>0.2288</v>
       </c>
       <c r="V23" t="n">
         <v>0.3776</v>
@@ -2287,7 +2287,7 @@
         <v>-19.4719</v>
       </c>
       <c r="F24" t="n">
-        <v>4.762799999999999</v>
+        <v>4.763</v>
       </c>
       <c r="G24" t="n">
         <v>-16.5436</v>
@@ -2299,7 +2299,7 @@
         <v>-12.9021</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.488600000000001</v>
+        <v>-4.488599999999999</v>
       </c>
       <c r="K24" t="n">
         <v>1.433799999999999</v>
@@ -2314,7 +2314,7 @@
         <v>-5.075100000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.979699999999999</v>
+        <v>-6.9797</v>
       </c>
       <c r="P24" t="n">
         <v>-3.8809</v>
@@ -2326,13 +2326,13 @@
         <v>13.5823</v>
       </c>
       <c r="S24" t="n">
-        <v>2.607699999999999</v>
+        <v>2.6077</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1068000000000002</v>
+        <v>-0.1067999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7143</v>
+        <v>2.7146</v>
       </c>
       <c r="V24" t="n">
         <v>3.1074</v>
